--- a/IBM.xlsx
+++ b/IBM.xlsx
@@ -3,10 +3,11 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <calcPr/>
   <extLst>
@@ -16,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="191">
   <si>
     <t>S.No</t>
   </si>
@@ -439,13 +440,210 @@
   </si>
   <si>
     <t xml:space="preserve">Add data handling, breach notification, and audit rights into the contract with IBM</t>
+  </si>
+  <si>
+    <t>Source</t>
+  </si>
+  <si>
+    <t>Destination</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Current Mechanism</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recommended Mechanism</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HR User</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Browser Application</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Username/password entered at login</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entra ID login (OIDC) with MFA enforced via Conditional Access</t>
+  </si>
+  <si>
+    <t xml:space="preserve">User's actual identity check should happen here, once</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color indexed="64"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t xml:space="preserve">Username/password passed through on </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color indexed="64"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>every</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color indexed="64"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t xml:space="preserve"> API call + JWT (client-provenance only)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">OAuth2/OIDC access token (short-lived), issued once at login by Entra ID; no raw credentials sent again after login</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Highest-priority fix — confirmed by IBM as current design</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JWT Validation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">App-issued JWT, validated by app's own logic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Validate Entra ID–issued token signature against Entra's public JWKS endpoint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moves trust from app-controlled secret to Entra ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure Blob Storage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Managed Identity (retain), scoped to least privilege (specific container only)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confirmed working pattern</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ingest Function</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Managed Identity (event trigger + read)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Managed Identity (retain), read-only where write isn't required</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Managed Identity via Entra ID authentication for MySQL, least-privilege DB role (not admin)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IBM confirmed read-write-update access is required</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Managed Identity (retain), scoped RBAC data-plane role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Same read-write-update scope confirmed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure Database for MySQL (RAG retrieval)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Managed Identity (retain), read-only role if only retrieval is needed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Separate role from Ingest Function's write role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cosmos DB (RAG retrieval)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Agents (via AI Foundry)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure SQL/MySQL &amp; Cosmos DB (context retrieval)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Managed Identity (retain), read-only</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Agents / FastAPI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">API key (planned)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color indexed="64"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t xml:space="preserve">Managed Identity / Entra ID authentication (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="64"/>
+        <rFont val="Courier New"/>
+      </rPr>
+      <t>DefaultAzureCredential</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color indexed="64"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t xml:space="preserve">) if supported; else API key stored in Key Vault with rotation</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">IBM was unsure this could be avoided — needs follow-up confirmation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure Key Vault (secrets/keys)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not fully defined</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Managed Identity, scoped RBAC access policy per service</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FastAPI Gateway / Agents</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phoenix (Tracing Container)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not specified</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Internal-network-only access (private VNet), authenticated trace export (e.g., API token or mTLS), no public endpoint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Currently undefined — needs to be closed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Future Headless Clients</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JWT (client-provenance)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Continue using JWT for client attestation; combine with OAuth2 client credentials flow if a real service-to-service caller is introduced</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Explicitly designed for future extensibility per IBM</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="11.000000"/>
       <color theme="1"/>
@@ -462,6 +660,11 @@
       <sz val="12.000000"/>
       <color indexed="64"/>
       <name val="Times New Roman"/>
+    </font>
+    <font>
+      <sz val="11.000000"/>
+      <color indexed="64"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -484,13 +687,22 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="2" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf fontId="2" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1966,4 +2178,323 @@
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="0" copies="1"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col customWidth="1" min="2" max="2" width="25.7109375"/>
+    <col customWidth="1" min="3" max="3" width="56.140625"/>
+    <col customWidth="1" min="4" max="4" width="57.57421875"/>
+    <col customWidth="1" min="5" max="5" width="78.7109375"/>
+    <col customWidth="1" min="6" max="6" width="48.7109375"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="60">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" ht="150">
+      <c r="A2" s="4">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="3" ht="240">
+      <c r="A3" s="4">
+        <v>2</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="4" ht="150">
+      <c r="A4" s="4">
+        <v>3</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="5" ht="135">
+      <c r="A5" s="4">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="6" ht="135">
+      <c r="A6" s="4">
+        <v>5</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" ht="180">
+      <c r="A7" s="4">
+        <v>6</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="8" ht="120">
+      <c r="A8" s="4">
+        <v>7</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="9" ht="120">
+      <c r="A9" s="4">
+        <v>8</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="10" ht="120">
+      <c r="A10" s="4">
+        <v>9</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="11" ht="105">
+      <c r="A11" s="4">
+        <v>10</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="12" ht="253.5">
+      <c r="A12" s="4">
+        <v>11</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="13" ht="120">
+      <c r="A13" s="4">
+        <v>12</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="14" ht="240">
+      <c r="A14" s="4">
+        <v>13</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="15" ht="285">
+      <c r="A15" s="4">
+        <v>14</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>190</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
+</worksheet>
 </file>